--- a/XlsxSharp.Tests/Resource/Other/PivotTableReferenceFiles/LongText/outputfile.xlsx
+++ b/XlsxSharp.Tests/Resource/Other/PivotTableReferenceFiles/LongText/outputfile.xlsx
@@ -1,34 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:workbookPr codeName="ThisWorkbook"/>
-  <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="0"/>
-  </x:bookViews>
-  <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <x:sheet name="pvt" sheetId="2" r:id="rId3"/>
-  </x:sheets>
-  <x:definedNames/>
-  <x:calcPr calcId="125725"/>
-  <x:pivotCaches>
-    <x:pivotCache cacheId="0" r:id="rId6"/>
-  </x:pivotCaches>
-</x:workbook>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView firstSheet="0" activeTab="0"/>
+  </bookViews>
+  <sheets>
+    <sheet r:id="rId1" name="Sheet1" sheetId="1"/>
+    <sheet r:id="rId2" name="pvt" sheetId="2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="125725"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId5"/>
+  </pivotCaches>
+</workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t>Col1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Col2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890</x:t>
-  </x:si>
-</x:sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <si>
+    <t>Col1</t>
+  </si>
+  <si>
+    <t>Col2</t>
+  </si>
+  <si>
+    <t>1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -80,7 +80,36 @@
 </styleSheet>
 </file>
 
-<file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3" saveData="1" refreshOnLoad="1">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields>
+    <cacheField name="Col1">
+      <sharedItems count="1" longText="1">
+        <s v="1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Col2">
+      <sharedItems count="1" containsNumber="1" containsInteger="1" minValue="2" maxValue="2" containsSemiMixedTypes="0" containsString="0">
+        <n v="2"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr">
+  <r>
+    <s v="1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890"/>
+    <n v="2"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="2">
@@ -104,14 +133,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B2" totalsRowShown="0">
-  <x:autoFilter ref="A1:B2"/>
-  <x:tableColumns count="2">
-    <x:tableColumn id="1" name="Col1"/>
-    <x:tableColumn id="2" name="Col2"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B2" totalsRowShown="0">
+  <autoFilter ref="A1:B2"/>
+  <tableColumns count="2">
+    <tableColumn id="1" name="Col1"/>
+    <tableColumn id="2" name="Col2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -398,81 +427,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1:B2"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData>
-    <x:row r="1" spans="1:2">
-      <x:c r="A1" s="0" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B1" s="0" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:2">
-      <x:c r="A2" s="0" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="1">
-    <x:tablePart r:id="rId7"/>
-  </x:tableParts>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId6"/>
+  </tableParts>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
-  <x:dimension ref="A1"/>
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
-</x:worksheet>
-</file>
-
-<file path=pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:pivotCacheDefinition xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r:id="rId1" saveData="1" refreshOnLoad="1" createdVersion="5" refreshedVersion="5" minRefreshableVersion="3">
-  <x:cacheSource type="worksheet">
-    <x:worksheetSource name="Table1"/>
-  </x:cacheSource>
-  <x:cacheFields>
-    <x:cacheField name="Col1">
-      <x:sharedItems count="1" longText="1">
-        <x:s v="1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890"/>
-      </x:sharedItems>
-    </x:cacheField>
-    <x:cacheField name="Col2">
-      <x:sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="2" count="1">
-        <x:n v="2"/>
-      </x:sharedItems>
-    </x:cacheField>
-  </x:cacheFields>
-</x:pivotCacheDefinition>
-</file>
-
-<file path=pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="xr">
-  <r>
-    <s v="1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890 1234567890"/>
-    <n v="2"/>
-  </r>
-</pivotCacheRecords>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="1" orientation="default" pageOrder="downThenOver" cellComments="none" errors="displayed" blackAndWhite="0" draft="0" scale="100"/>
+  <headerFooter/>
+  <tableParts count="0"/>
+</worksheet>
 </file>